--- a/缓存数据/farmeCsm.xlsx
+++ b/缓存数据/farmeCsm.xlsx
@@ -462,19 +462,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1645586.65</v>
+        <v>1703615.639999993</v>
       </c>
       <c r="C2" t="n">
-        <v>1320526.94</v>
+        <v>1378720.069999996</v>
       </c>
       <c r="D2" t="n">
-        <v>325059.7100000003</v>
+        <v>324895.5699999999</v>
       </c>
       <c r="E2" t="n">
-        <v>116329.05</v>
+        <v>112436.02</v>
       </c>
       <c r="F2" t="n">
-        <v>1529257.600000001</v>
+        <v>1591179.619999995</v>
       </c>
     </row>
     <row r="3">
@@ -484,19 +484,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1703615.639999996</v>
+        <v>1724072.27</v>
       </c>
       <c r="C3" t="n">
-        <v>1378720.069999997</v>
+        <v>1362777.650000002</v>
       </c>
       <c r="D3" t="n">
-        <v>324895.5699999999</v>
+        <v>361294.62</v>
       </c>
       <c r="E3" t="n">
-        <v>112436.02</v>
+        <v>131564.4600000001</v>
       </c>
       <c r="F3" t="n">
-        <v>1591179.619999996</v>
+        <v>1592507.81</v>
       </c>
     </row>
     <row r="4">
@@ -506,19 +506,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1724072.270000002</v>
+        <v>1734006.25</v>
       </c>
       <c r="C4" t="n">
-        <v>1362777.650000001</v>
+        <v>1361544.599999999</v>
       </c>
       <c r="D4" t="n">
-        <v>361294.62</v>
+        <v>372461.6499999998</v>
       </c>
       <c r="E4" t="n">
-        <v>131564.46</v>
+        <v>143197.3500000001</v>
       </c>
       <c r="F4" t="n">
-        <v>1592507.810000001</v>
+        <v>1590808.899999999</v>
       </c>
     </row>
     <row r="5">
@@ -528,19 +528,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1734006.250000001</v>
+        <v>1778373.000000002</v>
       </c>
       <c r="C5" t="n">
-        <v>1361544.599999999</v>
+        <v>1445744.96</v>
       </c>
       <c r="D5" t="n">
-        <v>372461.6499999998</v>
+        <v>332628.0399999999</v>
       </c>
       <c r="E5" t="n">
-        <v>143197.35</v>
+        <v>117963.72</v>
       </c>
       <c r="F5" t="n">
-        <v>1590808.9</v>
+        <v>1660409.280000001</v>
       </c>
     </row>
     <row r="6">
@@ -550,19 +550,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1778373.000000002</v>
+        <v>1855978.499999998</v>
       </c>
       <c r="C6" t="n">
-        <v>1445744.960000001</v>
+        <v>1544634.289999998</v>
       </c>
       <c r="D6" t="n">
-        <v>332628.0399999999</v>
+        <v>311344.2099999999</v>
       </c>
       <c r="E6" t="n">
-        <v>117963.72</v>
+        <v>111647.82</v>
       </c>
       <c r="F6" t="n">
-        <v>1660409.280000002</v>
+        <v>1744330.679999999</v>
       </c>
     </row>
     <row r="7">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1855978.500000002</v>
+        <v>1797287.420000001</v>
       </c>
       <c r="C7" t="n">
-        <v>1544634.29</v>
+        <v>1461846.640000001</v>
       </c>
       <c r="D7" t="n">
-        <v>311344.21</v>
+        <v>335440.7800000001</v>
       </c>
       <c r="E7" t="n">
-        <v>111647.82</v>
+        <v>138853.43</v>
       </c>
       <c r="F7" t="n">
-        <v>1744330.680000001</v>
+        <v>1658433.99</v>
       </c>
     </row>
     <row r="8">
@@ -594,19 +594,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1797287.420000003</v>
+        <v>1790071.349999998</v>
       </c>
       <c r="C8" t="n">
-        <v>1461846.640000001</v>
+        <v>1413893.9</v>
       </c>
       <c r="D8" t="n">
-        <v>335440.7800000001</v>
+        <v>376177.4500000007</v>
       </c>
       <c r="E8" t="n">
-        <v>138853.43</v>
+        <v>151009.44</v>
       </c>
       <c r="F8" t="n">
-        <v>1658433.990000003</v>
+        <v>1639061.909999999</v>
       </c>
     </row>
     <row r="9">
@@ -616,19 +616,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1790071.349999997</v>
+        <v>1864793.610000001</v>
       </c>
       <c r="C9" t="n">
-        <v>1413893.899999999</v>
+        <v>1457271.569999997</v>
       </c>
       <c r="D9" t="n">
-        <v>376177.4500000005</v>
+        <v>407522.0399999998</v>
       </c>
       <c r="E9" t="n">
-        <v>151009.44</v>
+        <v>176094.09</v>
       </c>
       <c r="F9" t="n">
-        <v>1639061.909999998</v>
+        <v>1688699.519999999</v>
       </c>
     </row>
   </sheetData>

--- a/缓存数据/farmeCsm.xlsx
+++ b/缓存数据/farmeCsm.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -53,18 +53,18 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -462,19 +462,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1703615.639999993</v>
+        <v>1960818.199999999</v>
       </c>
       <c r="C2" t="n">
-        <v>1378720.069999996</v>
+        <v>1737044.209999998</v>
       </c>
       <c r="D2" t="n">
-        <v>324895.5699999999</v>
+        <v>223773.99</v>
       </c>
       <c r="E2" t="n">
-        <v>112436.02</v>
+        <v>72609.56000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>1591179.619999995</v>
+        <v>1888208.639999999</v>
       </c>
     </row>
     <row r="3">
@@ -484,19 +484,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1724072.27</v>
+        <v>1981439.509999999</v>
       </c>
       <c r="C3" t="n">
-        <v>1362777.650000002</v>
+        <v>1765100.920000001</v>
       </c>
       <c r="D3" t="n">
-        <v>361294.62</v>
+        <v>216338.59</v>
       </c>
       <c r="E3" t="n">
-        <v>131564.4600000001</v>
+        <v>74878.58</v>
       </c>
       <c r="F3" t="n">
-        <v>1592507.81</v>
+        <v>1906560.929999999</v>
       </c>
     </row>
     <row r="4">
@@ -506,19 +506,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1734006.25</v>
+        <v>1869376.860000001</v>
       </c>
       <c r="C4" t="n">
-        <v>1361544.599999999</v>
+        <v>1674785.810000001</v>
       </c>
       <c r="D4" t="n">
-        <v>372461.6499999998</v>
+        <v>194591.0500000001</v>
       </c>
       <c r="E4" t="n">
-        <v>143197.3500000001</v>
+        <v>66779.48999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>1590808.899999999</v>
+        <v>1802597.370000002</v>
       </c>
     </row>
     <row r="5">
@@ -528,19 +528,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1778373.000000002</v>
+        <v>1814927.740000004</v>
       </c>
       <c r="C5" t="n">
-        <v>1445744.96</v>
+        <v>1601331.27</v>
       </c>
       <c r="D5" t="n">
-        <v>332628.0399999999</v>
+        <v>213596.4699999999</v>
       </c>
       <c r="E5" t="n">
-        <v>117963.72</v>
+        <v>86529.88</v>
       </c>
       <c r="F5" t="n">
-        <v>1660409.280000001</v>
+        <v>1728397.860000003</v>
       </c>
     </row>
     <row r="6">
@@ -550,19 +550,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1855978.499999998</v>
+        <v>1929221.129999999</v>
       </c>
       <c r="C6" t="n">
-        <v>1544634.289999998</v>
+        <v>1719702.240000001</v>
       </c>
       <c r="D6" t="n">
-        <v>311344.2099999999</v>
+        <v>209518.89</v>
       </c>
       <c r="E6" t="n">
-        <v>111647.82</v>
+        <v>88674.96999999997</v>
       </c>
       <c r="F6" t="n">
-        <v>1744330.679999999</v>
+        <v>1840546.159999999</v>
       </c>
     </row>
     <row r="7">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1797287.420000001</v>
+        <v>2063907.949999998</v>
       </c>
       <c r="C7" t="n">
-        <v>1461846.640000001</v>
+        <v>1870246.279999999</v>
       </c>
       <c r="D7" t="n">
-        <v>335440.7800000001</v>
+        <v>193661.6699999999</v>
       </c>
       <c r="E7" t="n">
-        <v>138853.43</v>
+        <v>85848.92999999996</v>
       </c>
       <c r="F7" t="n">
-        <v>1658433.99</v>
+        <v>1978059.019999997</v>
       </c>
     </row>
     <row r="8">
@@ -594,19 +594,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1790071.349999998</v>
+        <v>1924774.020000002</v>
       </c>
       <c r="C8" t="n">
-        <v>1413893.9</v>
+        <v>1749342.740000002</v>
       </c>
       <c r="D8" t="n">
-        <v>376177.4500000007</v>
+        <v>175431.2800000002</v>
       </c>
       <c r="E8" t="n">
-        <v>151009.44</v>
+        <v>73837.38</v>
       </c>
       <c r="F8" t="n">
-        <v>1639061.909999999</v>
+        <v>1850936.640000002</v>
       </c>
     </row>
     <row r="9">
@@ -616,22 +616,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1864793.610000001</v>
+        <v>1592349.500000002</v>
       </c>
       <c r="C9" t="n">
-        <v>1457271.569999997</v>
+        <v>1424746.669999999</v>
       </c>
       <c r="D9" t="n">
-        <v>407522.0399999998</v>
+        <v>167602.8299999999</v>
       </c>
       <c r="E9" t="n">
-        <v>176094.09</v>
+        <v>75787.29999999997</v>
       </c>
       <c r="F9" t="n">
-        <v>1688699.519999999</v>
+        <v>1516562.200000002</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>